--- a/jpcore-r4/feature/wg45-FamilyMember/CodeSystem-jp-siblingbirthorderbygender-cs.xlsx
+++ b/jpcore-r4/feature/wg45-FamilyMember/CodeSystem-jp-siblingbirthorderbygender-cs.xlsx
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>同胞内における性別の出生順名称を定義するCodeSystem。日本国内では、長女、長男、次女、次男など。性の多様性は、コード"#SBO_OTHER"を適用し、text要素に詳述。国際化対応は、designationにより出身国の用語を追加定義することで表現可能。</t>
+    <t>同胞内における性別の出生順名称を定義するCodeSystem。日本国内では、長女、長男、次女、次男など。十男・十女以上の出生順、性の多様性は、コード"#SBO_OTHER"を適用し、text要素に詳述。国際化対応は、designationにより出身国の用語を追加定義することで表現可能。</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -264,7 +264,7 @@
     <t>SBO_OTHER</t>
   </si>
   <si>
-    <t>その他（text要素に詳細を記載）</t>
+    <t>その他（十男・十女以上の出生順、性の多様性、その他の場合はtext要素に詳細を記載）</t>
   </si>
   <si>
     <t>SBO_NOS</t>
